--- a/docs/StructureDefinition-EncounterInpatient.xlsx
+++ b/docs/StructureDefinition-EncounterInpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatient.xlsx
+++ b/docs/StructureDefinition-EncounterInpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatient.xlsx
+++ b/docs/StructureDefinition-EncounterInpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
